--- a/fqhc-prospect-intelligence/tests/fixtures/uds_universal.xlsx
+++ b/fqhc-prospect-intelligence/tests/fixtures/uds_universal.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,22 +481,57 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Grant Number</t>
+          <t>GrantNumber</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Health Center Name</t>
+          <t>ReportingYear</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>HealthCenterName</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>HealthCenterStreetAddress</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>HealthCenterCity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>HealthCenterState</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>HealthCenterZIPCode</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ProjectDirector</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ProjectDirectorPhone</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ProjectDirectorEmail</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>UrbanRuralFlag</t>
         </is>
       </c>
     </row>
@@ -511,19 +546,112 @@
           <t>H80CS00123</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Erie Family Health Centers, Inc.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1701 W Superior St</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Chicago</t>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>60622</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Maria T Alvarez</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(312) 666-3494</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>malvarez@eriefamilyhealth.org</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>020020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H80CS00456</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Milwaukee Health Services Inc</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2555 N King Dr</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>53212</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Denise Whitaker</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>(414) 372-8080</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>dwhitaker@mhsi.org</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Urban</t>
         </is>
       </c>
     </row>
@@ -538,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,22 +677,397 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Grant Number</t>
+          <t>GrantNumber</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Total Patients</t>
+          <t>T3a_L1_Ca</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Male Patients</t>
+          <t>T3a_L1_Cb</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Female Patients</t>
+          <t>T3a_L2_Ca</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>T3a_L2_Cb</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>T3a_L3_Ca</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>T3a_L3_Cb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>T3a_L4_Ca</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>T3a_L4_Cb</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>T3a_L5_Ca</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>T3a_L5_Cb</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>T3a_L6_Ca</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>T3a_L6_Cb</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>T3a_L7_Ca</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>T3a_L7_Cb</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>T3a_L8_Ca</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>T3a_L8_Cb</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>T3a_L9_Ca</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>T3a_L9_Cb</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>T3a_L10_Ca</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>T3a_L10_Cb</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>T3a_L11_Ca</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>T3a_L11_Cb</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>T3a_L12_Ca</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>T3a_L12_Cb</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>T3a_L13_Ca</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>T3a_L13_Cb</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>T3a_L14_Ca</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>T3a_L14_Cb</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>T3a_L15_Ca</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>T3a_L15_Cb</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>T3a_L16_Ca</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>T3a_L16_Cb</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>T3a_L17_Ca</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>T3a_L17_Cb</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>T3a_L18_Ca</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>T3a_L18_Cb</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>T3a_L19_Ca</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>T3a_L19_Cb</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>T3a_L20_Ca</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>T3a_L20_Cb</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>T3a_L21_Ca</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>T3a_L21_Cb</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>T3a_L22_Ca</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>T3a_L22_Cb</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>T3a_L23_Ca</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>T3a_L23_Cb</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>T3a_L24_Ca</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>T3a_L24_Cb</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>T3a_L25_Ca</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>T3a_L25_Cb</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>T3a_L26_Ca</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>T3a_L26_Cb</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>T3a_L27_Ca</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>T3a_L27_Cb</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>T3a_L28_Ca</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>T3a_L28_Cb</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>T3a_L29_Ca</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>T3a_L29_Cb</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>T3a_L30_Ca</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>T3a_L30_Cb</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>T3a_L31_Ca</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>T3a_L31_Cb</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>T3a_L32_Ca</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>T3a_L32_Cb</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>T3a_L33_Ca</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>T3a_L33_Cb</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>T3a_L34_Ca</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>T3a_L34_Cb</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>T3a_L35_Ca</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>T3a_L35_Cb</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>T3a_L36_Ca</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>T3a_L36_Cb</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>T3a_L37_Ca</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>T3a_L37_Cb</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>T3a_L38_Ca</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>T3a_L38_Cb</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>T3a_L39_Ca</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>T3a_L39_Cb</t>
         </is>
       </c>
     </row>
@@ -580,13 +1083,484 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84532</v>
+        <v>12000</v>
       </c>
       <c r="D2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26532</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
         <v>33000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="CB2" t="n">
         <v>51532</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>020020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H80CS00456</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5104</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>10204</v>
       </c>
     </row>
   </sheetData>
@@ -600,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,11 +1588,6 @@
           <t>Total Patients Screened</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Patients With Diagnosis</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -628,9 +1597,6 @@
       </c>
       <c r="B2" t="n">
         <v>4120</v>
-      </c>
-      <c r="C2" t="n">
-        <v>900</v>
       </c>
     </row>
   </sheetData>
